--- a/DHKMontainApp/DONT-CHANGE-THIS.xlsx
+++ b/DHKMontainApp/DONT-CHANGE-THIS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17460"/>
+    <workbookView windowWidth="21000" windowHeight="16980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
-  <si>
-    <t>شركة جبال دهوك</t>
-  </si>
-  <si>
-    <t>لبيع الأحذية والشحاطات المستوردة</t>
-  </si>
-  <si>
-    <t>دهوك - مالطا - مقابل حديقة حيوانات</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>شــركــة  چیــــایئـــت  دهـــــوكــــێ</t>
+  </si>
+  <si>
+    <t>لبـيـــع الأحــذيــة  والشـحــاطــات المـستـــوردة</t>
+  </si>
+  <si>
+    <t>دهــوك - مـالـطــا - مـقـابــل حـديـقــة حـيــوانـات</t>
   </si>
   <si>
     <t>Date</t>
@@ -56,34 +56,40 @@
     <t>رقم قائمة</t>
   </si>
   <si>
-    <t>المبلغ</t>
-  </si>
-  <si>
-    <t>كارتون</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> السعر الزوج</t>
+    <t>مـبـلــغ كــلي</t>
+  </si>
+  <si>
+    <t>عـدد الكـراتـين</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> سـعــر الــزوج</t>
+  </si>
+  <si>
+    <t>عــدد ازواج</t>
+  </si>
+  <si>
+    <t>الـمــادة</t>
+  </si>
+  <si>
+    <t>boxcount</t>
+  </si>
+  <si>
+    <t>كـرتــون</t>
+  </si>
+  <si>
+    <t>couples</t>
   </si>
   <si>
     <t>زوج</t>
   </si>
   <si>
-    <t>المادة</t>
-  </si>
-  <si>
-    <t>boxcount</t>
-  </si>
-  <si>
-    <t>couples</t>
-  </si>
-  <si>
     <t>currency type</t>
   </si>
   <si>
     <t>Price</t>
   </si>
   <si>
-    <t>مجموع القائمة</t>
+    <t>مـجـمـوع القائـمـة</t>
   </si>
 </sst>
 </file>
@@ -96,7 +102,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,18 +118,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -684,137 +678,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -827,6 +821,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -857,19 +854,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -885,7 +873,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1151,16 +1139,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>471805</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>635</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>73660</xdr:colOff>
+      <xdr:colOff>400050</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>186690</xdr:rowOff>
+      <xdr:rowOff>26035</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1171,14 +1159,15 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
+        <a:srcRect l="5302" t="17851" r="3767" b="17553"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2162175" y="635"/>
-          <a:ext cx="1658620" cy="944880"/>
+          <a:off x="1390015" y="66675"/>
+          <a:ext cx="3296285" cy="718185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1451,14 +1440,11 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.71428571428571" style="1" customWidth="1"/>
-    <col min="2" max="3" width="10.7142857142857" style="1" customWidth="1"/>
-    <col min="4" max="5" width="10.1809523809524" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.6952380952381" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.9809523809524" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.2666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1.14285714285714" style="1" customWidth="1"/>
+    <col min="2" max="8" width="12.6285714285714" style="1" customWidth="1"/>
     <col min="9" max="9" width="11" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.14285714285714" style="2"/>
+    <col min="10" max="32" width="9.14285714285714" style="2"/>
+    <col min="33" max="16384" width="0.866666666666667" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8">
@@ -1497,200 +1483,218 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="2:2">
-      <c r="B5" s="1" t="s">
+    <row r="5" ht="15.5" customHeight="1" spans="2:8">
+      <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="2:2">
-      <c r="B6" s="1" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" ht="15.5" customHeight="1" spans="2:8">
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="2:2">
-      <c r="B7" s="1" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" ht="15.5" customHeight="1" spans="2:8">
+      <c r="B7" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" ht="23" customHeight="1" spans="2:8">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="6" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="21" customHeight="1" spans="2:7">
+    <row r="9" ht="21" customHeight="1" spans="2:8">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="2:8">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" ht="16" customHeight="1" spans="2:8">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" ht="16" customHeight="1" spans="2:8">
-      <c r="B12" s="12"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" ht="16" customHeight="1" spans="2:8">
-      <c r="B13" s="12"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" ht="16" customHeight="1" spans="2:8">
-      <c r="B14" s="12"/>
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" ht="16" customHeight="1" spans="2:8">
-      <c r="B15" s="12"/>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" ht="16" customHeight="1" spans="2:8">
-      <c r="B16" s="12"/>
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" ht="16" customHeight="1" spans="2:8">
-      <c r="B17" s="12"/>
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" ht="16" customHeight="1" spans="2:8">
-      <c r="B18" s="12"/>
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" ht="16" customHeight="1" spans="2:8">
-      <c r="B19" s="12"/>
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" ht="16" customHeight="1" spans="2:8">
-      <c r="B20" s="12"/>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" ht="16" customHeight="1" spans="2:8">
-      <c r="B21" s="12"/>
-      <c r="H21" s="13"/>
-    </row>
-    <row r="22" ht="16" customHeight="1" spans="2:8">
-      <c r="B22" s="12"/>
-      <c r="H22" s="13"/>
-    </row>
-    <row r="23" ht="16" customHeight="1" spans="2:8">
-      <c r="B23" s="12"/>
-      <c r="H23" s="13"/>
-    </row>
-    <row r="24" ht="16" customHeight="1" spans="2:8">
-      <c r="B24" s="12"/>
-      <c r="H24" s="13"/>
-    </row>
-    <row r="25" ht="16" customHeight="1" spans="2:8">
-      <c r="B25" s="12"/>
-      <c r="H25" s="13"/>
-    </row>
-    <row r="26" ht="16" customHeight="1" spans="2:8">
-      <c r="B26" s="12"/>
-      <c r="H26" s="13"/>
-    </row>
-    <row r="27" ht="16" customHeight="1" spans="2:8">
-      <c r="B27" s="12"/>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" ht="16" customHeight="1" spans="2:8">
-      <c r="B28" s="12"/>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29" ht="16" customHeight="1" spans="2:8">
-      <c r="B29" s="12"/>
-      <c r="H29" s="13"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" spans="2:8">
-      <c r="B30" s="12"/>
-      <c r="H30" s="13"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" spans="2:8">
-      <c r="B31" s="12"/>
-      <c r="H31" s="13"/>
-    </row>
-    <row r="32" ht="16" customHeight="1" spans="2:8">
-      <c r="B32" s="12"/>
-      <c r="H32" s="13"/>
-    </row>
-    <row r="33" ht="16" customHeight="1" spans="2:8">
-      <c r="B33" s="12"/>
-      <c r="H33" s="13"/>
-    </row>
-    <row r="34" ht="16" customHeight="1" spans="2:8">
-      <c r="B34" s="12"/>
-      <c r="H34" s="13"/>
-    </row>
-    <row r="35" ht="16" customHeight="1" spans="2:8">
-      <c r="B35" s="12"/>
-      <c r="H35" s="13"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:8">
-      <c r="A36" s="4"/>
-      <c r="B36" s="14" t="s">
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B12" s="13"/>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B13" s="13"/>
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B14" s="13"/>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B15" s="13"/>
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B16" s="13"/>
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B17" s="13"/>
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B18" s="13"/>
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B19" s="13"/>
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B20" s="13"/>
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B21" s="13"/>
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B22" s="13"/>
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B23" s="13"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B24" s="13"/>
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B25" s="13"/>
+      <c r="H25" s="14"/>
+    </row>
+    <row r="26" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B26" s="13"/>
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B27" s="13"/>
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B28" s="13"/>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B29" s="13"/>
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B30" s="13"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B31" s="13"/>
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" ht="17.5" customHeight="1" spans="2:8">
+      <c r="B32" s="13"/>
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" ht="17.5" customHeight="1" spans="1:8">
+      <c r="B33" s="13"/>
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" ht="17.5" customHeight="1" spans="1:8">
+      <c r="B34" s="13"/>
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" ht="13" customHeight="1" spans="1:8">
+      <c r="B35" s="13"/>
+      <c r="H35" s="14"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:8">
+      <c r="A36" s="5"/>
+      <c r="B36" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="14" t="s">
+      <c r="C36" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="15" t="s">
+      <c r="D36" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="E36" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="F36" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" ht="16" customHeight="1"/>
-    <row r="38" ht="17" customHeight="1" spans="5:5">
-      <c r="E38" s="18"/>
+      <c r="G36" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" ht="1" customHeight="1"/>
+    <row r="38" ht="17" customHeight="1" spans="1:8">
+      <c r="E38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="12">
